--- a/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,12</t>
+          <t>-1,58; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 1,73</t>
+          <t>-4,82; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 6,98</t>
+          <t>-9,72; 7,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,68</t>
+          <t>-0,66; 6,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,0</t>
+          <t>-6,71; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,57</t>
+          <t>-5,21; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 0,0</t>
+          <t>-38,42; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,0</t>
+          <t>-5,36; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,83</t>
+          <t>-2,49; 0,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,78</t>
+          <t>-1,66; 2,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 1,25</t>
+          <t>-3,05; 1,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 14,17</t>
+          <t>-1,89; 15,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,49; 367,57</t>
+          <t>-90,05; 573,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 288,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 0,0</t>
+          <t>-4,13; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,62</t>
+          <t>-1,0; 1,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 0,0</t>
+          <t>-3,68; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,21</t>
+          <t>-2,0; 4,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,75</t>
+          <t>-3,43; 6,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 0,0</t>
+          <t>-45,63; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,69</t>
+          <t>-0,79; 0,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,48</t>
+          <t>-1,25; 0,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,48</t>
+          <t>-1,61; 0,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 2,69</t>
+          <t>-5,68; 2,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-86,34; 344,34</t>
+          <t>-84,39; 351,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 82,3</t>
+          <t>-78,3; 83,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-80,07; 84,44</t>
+          <t>-77,1; 82,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-87,65; 242,3</t>
+          <t>-85,2; 175,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,09</t>
+          <t>-1,58; 3,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,73</t>
+          <t>-4,55; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 7,33</t>
+          <t>-10,54; 6,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 6,05</t>
+          <t>-0,64; 5,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 0,0</t>
+          <t>-5,31; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,57</t>
+          <t>-4,99; 0,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 0,0</t>
+          <t>-42,27; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,0</t>
+          <t>-5,44; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,82</t>
+          <t>-2,42; 0,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,06</t>
+          <t>-2,02; 1,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,33</t>
+          <t>-3,04; 1,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 15,49</t>
+          <t>-2,38; 13,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,05; 573,71</t>
+          <t>-100,0; 531,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 290,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,61</t>
+          <t>-1,0; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 0,0</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,92</t>
+          <t>-2,0; 4,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 6,52</t>
+          <t>-3,32; 6,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 0,0</t>
+          <t>-45,4; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,72</t>
+          <t>-0,77; 0,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,49</t>
+          <t>-1,28; 0,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,56</t>
+          <t>-1,56; 0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 2,85</t>
+          <t>-5,61; 2,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,39; 351,88</t>
+          <t>-84,44; 461,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 83,8</t>
+          <t>-78,4; 101,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-77,1; 82,31</t>
+          <t>-74,91; 97,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-85,2; 175,42</t>
+          <t>-87,52; 234,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,19</t>
+          <t>-1,57; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,73</t>
+          <t>-3,77; 1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 6,66</t>
+          <t>-8,64; 7,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-9,35</t>
+          <t>-10,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,87</t>
+          <t>-0,66; 5,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,0</t>
+          <t>-5,3; 0,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 0,58</t>
+          <t>-5,26; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 0,0</t>
+          <t>-38,99; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,0</t>
+          <t>-6,23; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>169,52%</t>
+          <t>204,23%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,82</t>
+          <t>-2,39; 0,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,95</t>
+          <t>-1,93; 1,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,41</t>
+          <t>-3,43; 1,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 13,96</t>
+          <t>-1,75; 15,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 531,11</t>
+          <t>-88,49; 367,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 290,63</t>
+          <t>-100,0; 288,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-4,7; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,07</t>
+          <t>-1,02; 1,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-16,46</t>
+          <t>-18,23</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,83</t>
+          <t>-1,99; 5,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 6,56</t>
+          <t>-3,33; 5,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 0,0</t>
+          <t>-46,89; 0,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-1,18</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-25,61%</t>
+          <t>-28,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,77</t>
+          <t>-0,81; 0,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,49</t>
+          <t>-1,3; 0,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,48</t>
+          <t>-1,51; 0,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 2,83</t>
+          <t>-6,56; 2,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 461,41</t>
+          <t>-86,34; 344,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-78,4; 101,87</t>
+          <t>-78,95; 82,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-74,91; 97,81</t>
+          <t>-80,07; 84,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 234,53</t>
+          <t>-89,03; 234,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,169 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-26,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.8389802626506763</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1849916083875369</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.306255876170838</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.5557862444379419</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.2359792698551488</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.2633034368999337</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1705078580652446</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,39</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 3,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-3,77; 1,73</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 7,61</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.57187290816248</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.774419693250326</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.636379652568815</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.390482379787681</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.120287644687806</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.734808760574003</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.612350833869808</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-10,17</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>211,24%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-66,53%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 5,68</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,3; 0,0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,26; 0,57</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-38,99; 0,0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.354542726710588</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.713572622313287</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.120792577373895</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-10.17151971930686</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>2.112379211358793</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.6652590644694186</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,78</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.6552126004510767</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.301055096131676</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.255610112936573</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-38.99356604177093</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 0,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.683511323307728</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5705655363610553</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +789,157 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-55,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-34,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>204,23%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.78387776309009</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,39; 0,83</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,93; 1,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,43; 1,25</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,75; 15,05</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-88,49; 367,57</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 288,05</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-6.22964899907841</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-4,7; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,02; 1,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,62; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.5206088406114094</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.05570338818941169</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.6310259479277105</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.390425280055253</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.558084631483615</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.04163031556633918</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3487855054848457</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>2.042265789823584</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-18,23</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,33%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.390154436513509</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.927085033938905</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.427420071173693</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.748952454420001</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.8849001652130731</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 5,21</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 5,75</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-46,89; 0,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8250841052763431</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.778972885841784</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.245949222560291</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>15.05180940629017</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>3.675666355838989</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.880509957079701</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +947,253 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-6,96%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-33,01%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-35,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-28,85%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>-1.358459749449427</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.03745604633860911</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.03660002975034</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.07606566930703439</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 0,69</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-1,3; 0,48</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,48</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-6,56; 2,68</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-86,34; 344,34</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-78,95; 82,3</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-80,07; 84,44</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-89,03; 234,05</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.702284181696479</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.015449733333206</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.616387996964967</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.620413744849848</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.4710432920911957</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>1.115267202851117</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-18.22674017021749</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="n">
+        <v>0.4763871645981081</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.5033453893848913</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>-1.993611461221916</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-3.327168591487586</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-46.89299712719271</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>5.212233705119643</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>5.751489485341557</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.04141029203507145</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.3857855427943032</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.4869394756528936</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-1.184590916046651</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.0696131937988918</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.3300578541134724</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.3509410150506869</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.2884855942588007</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.8148087745654379</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.30083163329433</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-1.510665155345928</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-6.564098830040333</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.8634097646184045</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.7895146409163312</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.8006712673468896</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.89032960570763</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.6875861175190938</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4840816859589436</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.4835398451937005</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.680263942389844</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>3.443369764564115</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.8230405021209716</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8443560204750292</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>2.340513244378927</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1201,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
